--- a/ITI/MHD/StructureDefinition-IHE.MHD.Comprehensive.Folder.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.Comprehensive.Folder.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$42</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="362">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -646,6 +646,25 @@
 </t>
   </si>
   <si>
+    <t>List.extension:homeCommunityId</t>
+  </si>
+  <si>
+    <t>homeCommunityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/ITI/MHD/StructureDefinition/ihe-HomeCommunityId}
+</t>
+  </si>
+  <si>
+    <t>The homeCommunityId where the artifact resides</t>
+  </si>
+  <si>
+    <t>The globally unique, immutable, identifier of the homeCommunityId entity where this artifact resides. The format of the value is an OID.</t>
+  </si>
+  <si>
+    <t>Folder.homeCommunityId</t>
+  </si>
+  <si>
     <t>List.modifierExtension</t>
   </si>
   <si>
@@ -665,7 +684,7 @@
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:use}
+    <t xml:space="preserve">value:type}
 </t>
   </si>
   <si>
@@ -688,6 +707,12 @@
 </t>
   </si>
   <si>
+    <t>Folder.uniqueId</t>
+  </si>
+  <si>
+    <t>The XDS UniqueId for the Folder. Globally unique identifier for the Folder.</t>
+  </si>
+  <si>
     <t>List.identifier:entryUUID</t>
   </si>
   <si>
@@ -696,6 +721,12 @@
   <si>
     <t xml:space="preserve">Identifier {https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.EntryUUID.Identifier}
 </t>
+  </si>
+  <si>
+    <t>Folder.entryUUID</t>
+  </si>
+  <si>
+    <t>The XDS entryUUID for the Folder. A globally unique identifier used to identify the XDS Folder entry in ebRIM.</t>
   </si>
   <si>
     <t>List.status</t>
@@ -1455,12 +1486,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM41"/>
+  <dimension ref="A1:AM42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="25.703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.98046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="23.53125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.1484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -3499,9 +3530,11 @@
         <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>81</v>
       </c>
@@ -3510,25 +3543,25 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3579,7 +3612,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3588,13 +3621,13 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>118</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>81</v>
@@ -3605,10 +3638,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3619,25 +3652,25 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3676,17 +3709,19 @@
         <v>81</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3698,28 +3733,26 @@
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>81</v>
       </c>
@@ -3728,10 +3761,10 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>81</v>
@@ -3740,13 +3773,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3785,19 +3818,17 @@
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3812,24 +3843,24 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>81</v>
@@ -3839,7 +3870,7 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>90</v>
@@ -3851,13 +3882,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3908,7 +3939,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3926,51 +3957,51 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -3995,13 +4026,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -4019,13 +4050,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -4034,13 +4065,13 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4082,9 +4113,7 @@
       <c r="N24" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="O24" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4093,28 +4122,28 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="T24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4147,21 +4176,21 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>236</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4178,21 +4207,23 @@
         <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>240</v>
       </c>
@@ -4204,10 +4235,10 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>81</v>
@@ -4219,13 +4250,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -4243,10 +4274,10 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>89</v>
@@ -4258,21 +4289,21 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4295,19 +4326,17 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>245</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -4317,10 +4346,10 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>81</v>
@@ -4332,11 +4361,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4354,7 +4385,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4375,15 +4406,15 @@
         <v>253</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
         <v>254</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4397,7 +4428,7 @@
         <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>81</v>
@@ -4406,19 +4437,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -4428,7 +4459,7 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>81</v>
@@ -4443,13 +4474,11 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4467,7 +4496,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4482,21 +4511,21 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4504,31 +4533,35 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -4576,7 +4609,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4591,21 +4624,21 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4616,7 +4649,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -4625,23 +4658,19 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -4689,7 +4718,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4704,32 +4733,32 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>280</v>
+        <v>81</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -4802,7 +4831,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4817,25 +4846,25 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>107</v>
+        <v>286</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4851,22 +4880,22 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -4891,13 +4920,13 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -4915,7 +4944,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4933,18 +4962,18 @@
         <v>107</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>81</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4955,7 +4984,7 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -4967,16 +4996,20 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>297</v>
+        <v>255</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5000,13 +5033,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -5024,13 +5057,13 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
@@ -5039,10 +5072,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>300</v>
+        <v>107</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5050,10 +5083,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5064,7 +5097,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5076,17 +5109,15 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5135,7 +5166,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5144,16 +5175,16 @@
         <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
@@ -5161,10 +5192,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5175,7 +5206,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -5187,15 +5218,17 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5244,25 +5277,25 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>106</v>
+        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>107</v>
+        <v>318</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5270,21 +5303,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -5296,17 +5329,15 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5355,19 +5386,19 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
@@ -5381,14 +5412,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>312</v>
+        <v>109</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5401,26 +5432,24 @@
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>111</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>112</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O36" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -5468,7 +5497,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>117</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5486,7 +5515,7 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
@@ -5494,45 +5523,45 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>245</v>
+        <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>320</v>
+        <v>113</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -5557,13 +5586,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -5581,25 +5610,25 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
@@ -5607,10 +5636,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5627,76 +5656,74 @@
         <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>325</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="P38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q38" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="R38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5705,7 +5732,7 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -5714,7 +5741,7 @@
         <v>107</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>332</v>
+        <v>245</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -5722,10 +5749,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5742,72 +5769,76 @@
         <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q39" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="R39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="P39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5816,7 +5847,7 @@
         <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
@@ -5825,7 +5856,7 @@
         <v>107</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
@@ -5833,10 +5864,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5844,10 +5875,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -5859,16 +5890,18 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -5916,10 +5949,10 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>89</v>
@@ -5931,10 +5964,10 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>342</v>
+        <v>107</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
@@ -5942,10 +5975,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5953,10 +5986,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -5968,20 +6001,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>245</v>
+        <v>349</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6005,13 +6034,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6029,32 +6058,145 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK42" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AL42" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM41">
+  <autoFilter ref="A1:AM42">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6064,7 +6206,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI40">
+  <conditionalFormatting sqref="A2:AI41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.Comprehensive.Folder.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.Comprehensive.Folder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
